--- a/data/trans_orig/P24C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144675</t>
+          <t>144507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182142</t>
+          <t>180871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82502</t>
+          <t>82111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106106</t>
+          <t>106153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235169</t>
+          <t>233831</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278646</t>
+          <t>276646</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87344</t>
+          <t>88611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121816</t>
+          <t>122558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42936</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65851</t>
+          <t>64929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137043</t>
+          <t>138662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>178396</t>
+          <t>180562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39176</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65777</t>
+          <t>65450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23603</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50807</t>
+          <t>52207</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80591</t>
+          <t>82448</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155498</t>
+          <t>153434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>195229</t>
+          <t>194064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72880</t>
+          <t>73104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102616</t>
+          <t>103621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237655</t>
+          <t>237134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>288057</t>
+          <t>286471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>141955</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>180710</t>
+          <t>182415</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78243</t>
+          <t>79829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108948</t>
+          <t>109594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>229076</t>
+          <t>230039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281299</t>
+          <t>281426</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54959</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85705</t>
+          <t>88085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59989</t>
+          <t>59699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95379</t>
+          <t>95927</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134836</t>
+          <t>135606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77360</t>
+          <t>78432</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109128</t>
+          <t>111062</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49550</t>
+          <t>49278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73469</t>
+          <t>73720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>135837</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174915</t>
+          <t>175125</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,38%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70296</t>
+          <t>71274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100598</t>
+          <t>103521</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49513</t>
+          <t>49440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74539</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129843</t>
+          <t>127450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168393</t>
+          <t>167818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59308</t>
+          <t>58293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89124</t>
+          <t>90402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>36834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60199</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102701</t>
+          <t>102971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141332</t>
+          <t>140265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>151239</t>
+          <t>152640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189667</t>
+          <t>191275</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88133</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>121909</t>
+          <t>124115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>249125</t>
+          <t>247874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300023</t>
+          <t>301785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140397</t>
+          <t>140187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177907</t>
+          <t>179222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121984</t>
+          <t>119926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155456</t>
+          <t>157466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>269915</t>
+          <t>270850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>324295</t>
+          <t>322890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62012</t>
+          <t>61347</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93334</t>
+          <t>92337</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47257</t>
+          <t>46124</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75336</t>
+          <t>75522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114813</t>
+          <t>117592</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>158019</t>
+          <t>157986</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>563792</t>
+          <t>563606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>639292</t>
+          <t>636307</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317656</t>
+          <t>318528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>374861</t>
+          <t>378223</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898567</t>
+          <t>900423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>996624</t>
+          <t>995130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>472035</t>
+          <t>474465</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>546227</t>
+          <t>545618</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>322346</t>
+          <t>319714</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>378871</t>
+          <t>375955</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>813423</t>
+          <t>810310</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>907251</t>
+          <t>905506</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>243911</t>
+          <t>243775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>304309</t>
+          <t>305297</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>142891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190037</t>
+          <t>189219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396724</t>
+          <t>405834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>475745</t>
+          <t>484202</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54083</t>
+          <t>54978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36930</t>
+          <t>38543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53175</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84040</t>
+          <t>83916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109219</t>
+          <t>111405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144867</t>
+          <t>145785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69733</t>
+          <t>68818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96526</t>
+          <t>94690</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188190</t>
+          <t>187104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>230695</t>
+          <t>229387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85049</t>
+          <t>81264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117441</t>
+          <t>115563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40935</t>
+          <t>40325</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65940</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>132922</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>174111</t>
+          <t>172897</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52058</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84444</t>
+          <t>85056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30663</t>
+          <t>32230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70496</t>
+          <t>71176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107812</t>
+          <t>107629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>157788</t>
+          <t>158967</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>199571</t>
+          <t>199264</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>139091</t>
+          <t>139265</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172548</t>
+          <t>174106</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>307617</t>
+          <t>310269</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>361721</t>
+          <t>362534</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137477</t>
+          <t>138255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178876</t>
+          <t>178413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97231</t>
+          <t>97728</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131130</t>
+          <t>132215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245367</t>
+          <t>245616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>298396</t>
+          <t>299339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41021</t>
+          <t>42079</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69513</t>
+          <t>69729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58035</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82236</t>
+          <t>81048</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118487</t>
+          <t>119152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123384</t>
+          <t>124725</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160045</t>
+          <t>161545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85460</t>
+          <t>86398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117593</t>
+          <t>117943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221982</t>
+          <t>222531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>268241</t>
+          <t>270031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94521</t>
+          <t>94072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131654</t>
+          <t>131920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67136</t>
+          <t>67264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100672</t>
+          <t>98998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173198</t>
+          <t>171201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219959</t>
+          <t>218075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56839</t>
+          <t>57526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89058</t>
+          <t>87391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59308</t>
+          <t>61151</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99868</t>
+          <t>100558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141241</t>
+          <t>140629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154120</t>
+          <t>153738</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193735</t>
+          <t>194111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118082</t>
+          <t>118312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152804</t>
+          <t>151689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284183</t>
+          <t>283270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335083</t>
+          <t>334404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97581</t>
+          <t>97224</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134033</t>
+          <t>135441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>94584</t>
+          <t>93863</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>128783</t>
+          <t>127125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>200219</t>
+          <t>200920</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>249932</t>
+          <t>251082</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209175</t>
+          <t>208335</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265597</t>
+          <t>268875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117604</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163261</t>
+          <t>162324</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>338066</t>
+          <t>338507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>410611</t>
+          <t>410605</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>585405</t>
+          <t>585344</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>663028</t>
+          <t>664426</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>446884</t>
+          <t>442571</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>508856</t>
+          <t>508273</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1047935</t>
+          <t>1047411</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1146631</t>
+          <t>1147182</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>448098</t>
+          <t>447789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>518478</t>
+          <t>524096</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>327527</t>
+          <t>326717</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>389445</t>
+          <t>391436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>797125</t>
+          <t>794606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>897632</t>
+          <t>892970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016 (tasa de respuesta: 97,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>23531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45672</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39495</t>
+          <t>37737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65909</t>
+          <t>66608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120741</t>
+          <t>119516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>152292</t>
+          <t>154099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76263</t>
+          <t>77152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101002</t>
+          <t>101793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204964</t>
+          <t>203528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245230</t>
+          <t>246153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65083</t>
+          <t>64492</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95756</t>
+          <t>95218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43463</t>
+          <t>44406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66939</t>
+          <t>68273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115997</t>
+          <t>114892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>154977</t>
+          <t>155677</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56215</t>
+          <t>54539</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37392</t>
+          <t>38492</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52772</t>
+          <t>53860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85322</t>
+          <t>85514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>150359</t>
+          <t>149981</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>189556</t>
+          <t>188344</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112541</t>
+          <t>111538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143677</t>
+          <t>143952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>269158</t>
+          <t>273292</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>321427</t>
+          <t>323648</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99205</t>
+          <t>97878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136508</t>
+          <t>134412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89627</t>
+          <t>88534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119569</t>
+          <t>120847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198946</t>
+          <t>196956</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248901</t>
+          <t>244518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>39107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66860</t>
+          <t>67478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>46924</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70973</t>
+          <t>70480</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107110</t>
+          <t>103416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137578</t>
+          <t>138114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174975</t>
+          <t>173653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94451</t>
+          <t>94967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125649</t>
+          <t>125341</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241356</t>
+          <t>242199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289165</t>
+          <t>289269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84121</t>
+          <t>83836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118736</t>
+          <t>117855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63179</t>
+          <t>64445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91472</t>
+          <t>93191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154753</t>
+          <t>155840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200616</t>
+          <t>200675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65398</t>
+          <t>64854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55304</t>
+          <t>55517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76312</t>
+          <t>76685</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111646</t>
+          <t>113385</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93261</t>
+          <t>92392</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125620</t>
+          <t>124394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82824</t>
+          <t>81993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113995</t>
+          <t>113922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186578</t>
+          <t>183816</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228971</t>
+          <t>228189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102601</t>
+          <t>105274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137366</t>
+          <t>137446</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98991</t>
+          <t>100204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131826</t>
+          <t>132525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>213027</t>
+          <t>213345</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>257358</t>
+          <t>258896</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152920</t>
+          <t>151377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203002</t>
+          <t>202916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104927</t>
+          <t>101245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>143298</t>
+          <t>141787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268494</t>
+          <t>265747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338442</t>
+          <t>332982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>533918</t>
+          <t>536944</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>604550</t>
+          <t>607611</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>398215</t>
+          <t>396063</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>456641</t>
+          <t>454198</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>950462</t>
+          <t>946894</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1044514</t>
+          <t>1038487</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>384577</t>
+          <t>382325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>449395</t>
+          <t>450863</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>324188</t>
+          <t>322678</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>380648</t>
+          <t>380689</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>725189</t>
+          <t>728954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>814550</t>
+          <t>816917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>144507</t>
+          <t>141824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180871</t>
+          <t>177948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82111</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106153</t>
+          <t>105833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>233831</t>
+          <t>234917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276646</t>
+          <t>278961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88611</t>
+          <t>89856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122558</t>
+          <t>124128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41909</t>
+          <t>42701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64929</t>
+          <t>66040</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138662</t>
+          <t>138465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180562</t>
+          <t>181038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38206</t>
+          <t>40170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65450</t>
+          <t>65583</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52207</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82448</t>
+          <t>80599</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153434</t>
+          <t>154072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194064</t>
+          <t>194159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73104</t>
+          <t>74102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103621</t>
+          <t>104462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237134</t>
+          <t>234762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>286471</t>
+          <t>288139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141955</t>
+          <t>142757</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>182415</t>
+          <t>180874</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79829</t>
+          <t>78754</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109594</t>
+          <t>109605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>230039</t>
+          <t>227824</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281426</t>
+          <t>280480</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55721</t>
+          <t>53630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88085</t>
+          <t>87238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33233</t>
+          <t>33385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59699</t>
+          <t>58895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95927</t>
+          <t>97419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135606</t>
+          <t>134948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78432</t>
+          <t>76976</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111062</t>
+          <t>109169</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49278</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73720</t>
+          <t>74660</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>135837</t>
+          <t>134397</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175125</t>
+          <t>174545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71274</t>
+          <t>71127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103521</t>
+          <t>102790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49440</t>
+          <t>48985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73136</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127450</t>
+          <t>130364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167818</t>
+          <t>167645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58293</t>
+          <t>59220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>88644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36834</t>
+          <t>37034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60829</t>
+          <t>60917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102971</t>
+          <t>103408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140265</t>
+          <t>141262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152640</t>
+          <t>151573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191275</t>
+          <t>190816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>88801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124115</t>
+          <t>122667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>247874</t>
+          <t>248815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301785</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>140187</t>
+          <t>139485</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179222</t>
+          <t>178354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119926</t>
+          <t>120894</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157466</t>
+          <t>156156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270850</t>
+          <t>270425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322890</t>
+          <t>322183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61347</t>
+          <t>62888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92337</t>
+          <t>94047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46124</t>
+          <t>45926</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75522</t>
+          <t>74111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117592</t>
+          <t>115718</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157986</t>
+          <t>158535</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>563606</t>
+          <t>565477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>636307</t>
+          <t>633093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318528</t>
+          <t>319953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>378223</t>
+          <t>377136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>900423</t>
+          <t>899861</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>995130</t>
+          <t>994652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>474465</t>
+          <t>472753</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>545618</t>
+          <t>546653</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319714</t>
+          <t>317181</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>375955</t>
+          <t>374681</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>810310</t>
+          <t>810633</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>905506</t>
+          <t>906603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>243775</t>
+          <t>244946</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>305297</t>
+          <t>302760</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142891</t>
+          <t>144247</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189219</t>
+          <t>190601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405834</t>
+          <t>402578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>484202</t>
+          <t>480266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54978</t>
+          <t>53686</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38543</t>
+          <t>37111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83916</t>
+          <t>82767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111405</t>
+          <t>109653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145785</t>
+          <t>143002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68818</t>
+          <t>69509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94690</t>
+          <t>95984</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187104</t>
+          <t>188217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229387</t>
+          <t>228454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81264</t>
+          <t>84621</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115563</t>
+          <t>117694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40325</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64989</t>
+          <t>66412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>133391</t>
+          <t>133952</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172897</t>
+          <t>174637</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53117</t>
+          <t>50856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85056</t>
+          <t>83815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71176</t>
+          <t>70233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107629</t>
+          <t>105940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>158967</t>
+          <t>160866</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>199264</t>
+          <t>202202</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>139265</t>
+          <t>137248</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>174106</t>
+          <t>172514</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>310269</t>
+          <t>310503</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>362534</t>
+          <t>363675</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138255</t>
+          <t>135883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178413</t>
+          <t>178417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97728</t>
+          <t>96069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132215</t>
+          <t>129227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245616</t>
+          <t>243433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299339</t>
+          <t>296542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42079</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69729</t>
+          <t>68516</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>33123</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58433</t>
+          <t>57293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81048</t>
+          <t>83510</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119152</t>
+          <t>119727</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124725</t>
+          <t>124294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161545</t>
+          <t>163637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86398</t>
+          <t>85491</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117943</t>
+          <t>117336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222531</t>
+          <t>220732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270031</t>
+          <t>270143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94072</t>
+          <t>95690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131920</t>
+          <t>132279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67264</t>
+          <t>68268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98998</t>
+          <t>99388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171201</t>
+          <t>170262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218075</t>
+          <t>219758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57526</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87391</t>
+          <t>87166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>61416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100558</t>
+          <t>100680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140629</t>
+          <t>140709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153738</t>
+          <t>154679</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194111</t>
+          <t>195290</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118312</t>
+          <t>119159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151689</t>
+          <t>152234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283270</t>
+          <t>285225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334404</t>
+          <t>335760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97224</t>
+          <t>95948</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135441</t>
+          <t>135508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93863</t>
+          <t>94181</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>127125</t>
+          <t>128450</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>200920</t>
+          <t>201045</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>251082</t>
+          <t>247679</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208335</t>
+          <t>207140</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268875</t>
+          <t>267054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>117199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>162324</t>
+          <t>162056</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>338507</t>
+          <t>338756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>410605</t>
+          <t>412082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>585344</t>
+          <t>582646</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>664426</t>
+          <t>662657</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>442571</t>
+          <t>445468</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>508273</t>
+          <t>509000</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1047411</t>
+          <t>1048377</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1147182</t>
+          <t>1150002</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>447789</t>
+          <t>450037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>524096</t>
+          <t>522206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>326717</t>
+          <t>331626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>391436</t>
+          <t>392608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>794606</t>
+          <t>799820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>892970</t>
+          <t>894166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>23710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45988</t>
+          <t>45889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27423</t>
+          <t>26543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37737</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66608</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119516</t>
+          <t>119932</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154099</t>
+          <t>152019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77152</t>
+          <t>75845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101793</t>
+          <t>103056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203528</t>
+          <t>206003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246153</t>
+          <t>245815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,7%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64492</t>
+          <t>64707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95218</t>
+          <t>93741</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44406</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68273</t>
+          <t>69183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114892</t>
+          <t>115815</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155677</t>
+          <t>153235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28846</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>55290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38492</t>
+          <t>38659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53860</t>
+          <t>53184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85514</t>
+          <t>85374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149981</t>
+          <t>148650</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>188344</t>
+          <t>187355</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>111538</t>
+          <t>111326</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143952</t>
+          <t>144738</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>273292</t>
+          <t>270665</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>323648</t>
+          <t>321999</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97878</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134412</t>
+          <t>136526</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88534</t>
+          <t>88102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120847</t>
+          <t>120583</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196956</t>
+          <t>198034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244518</t>
+          <t>246348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,95%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67478</t>
+          <t>69003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>47766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70480</t>
+          <t>70993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103416</t>
+          <t>105788</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138114</t>
+          <t>138632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>173653</t>
+          <t>173242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94967</t>
+          <t>95181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125341</t>
+          <t>124457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242199</t>
+          <t>242533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289269</t>
+          <t>288425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83836</t>
+          <t>84815</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117855</t>
+          <t>117310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64445</t>
+          <t>62839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93191</t>
+          <t>91253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155840</t>
+          <t>155342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200675</t>
+          <t>200021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>38030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64854</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55517</t>
+          <t>55085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76685</t>
+          <t>77090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113385</t>
+          <t>112085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92392</t>
+          <t>93416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124394</t>
+          <t>127010</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81993</t>
+          <t>82034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113922</t>
+          <t>114920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183816</t>
+          <t>185405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228189</t>
+          <t>228825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>105274</t>
+          <t>102916</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137446</t>
+          <t>136761</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100204</t>
+          <t>98841</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132525</t>
+          <t>131318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>213345</t>
+          <t>213172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>258896</t>
+          <t>256637</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151377</t>
+          <t>151388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202916</t>
+          <t>204390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101245</t>
+          <t>104924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>141787</t>
+          <t>144678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>265747</t>
+          <t>267512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>332982</t>
+          <t>332201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536944</t>
+          <t>532492</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>607611</t>
+          <t>605891</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>396063</t>
+          <t>391254</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>454198</t>
+          <t>454237</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>946894</t>
+          <t>950975</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1038487</t>
+          <t>1040076</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>382325</t>
+          <t>379365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>450863</t>
+          <t>448964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>322678</t>
+          <t>321357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>380689</t>
+          <t>381857</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>728954</t>
+          <t>725046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>816917</t>
+          <t>814744</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
